--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260618_215853.xlsx
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
